--- a/回後買上漲圖表_20260615/回後買上漲_嚴格版(1+2+3)_20260615.xlsx
+++ b/回後買上漲圖表_20260615/回後買上漲_嚴格版(1+2+3)_20260615.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,28 +561,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4721.TWO</t>
+          <t>2903.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>101</v>
+        <v>23.85</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>23.35</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4665</v>
+        <v>4753</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1619</v>
+        <v>1586</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -603,28 +603,28 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>4976.TW</t>
+          <t>2887.TW</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>34.6</v>
+        <v>30.2</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>34.05</v>
+        <v>28.9</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2917</v>
+        <v>157208</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>1157</v>
+        <v>64850</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
@@ -645,28 +645,28 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3093.TWO</t>
+          <t>8105.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.7</v>
+        <v>22.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>62.4</v>
+        <v>21.45</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3458</v>
+        <v>41248</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1563</v>
+        <v>17369</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>6166.TW</t>
+          <t>2204.TW</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>中華</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>141</v>
+        <v>56.6</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>134.5</v>
+        <v>55.9</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>3680</v>
+        <v>1855</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>2210</v>
+        <v>791</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
@@ -729,40 +729,418 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>6788.TWO</t>
+          <t>1307.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>449</v>
+        <v>36.75</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>428</v>
+        <v>35.6</v>
       </c>
       <c r="E6" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2834</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1342.TW</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>八貫</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>2096</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>1188</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6153.TW</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>嘉聯益</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>28567</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>15746</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>3322.TWO</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>建舜電</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>2077</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>1194</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="F9" s="11" t="n">
+        <v>2628</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>1573</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1808.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>潤隆</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2393.TW</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>億光</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>5528</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6196.TW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>548</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3889</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2348</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>踩20MA</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>1434.TW</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>福懋</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>2237</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>1418</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2851.TW</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>中再保</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1902</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1171</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>6409.TW</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>旭隼</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>930</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>874</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>1519</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>925</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -775,6 +1153,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
